--- a/artfynd/A 35419-2024 artfynd.xlsx
+++ b/artfynd/A 35419-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119253676</v>
+        <v>119253683</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119253637</v>
+        <v>119253676</v>
       </c>
       <c r="B3" t="n">
-        <v>97941</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119254435</v>
+        <v>119253663</v>
       </c>
       <c r="B4" t="n">
-        <v>57679</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,33 +900,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartnäset, Jmt</t>
@@ -983,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119253663</v>
+        <v>119254435</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,24 +1007,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartnäset, Jmt</t>
@@ -1095,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,12 +1115,7 @@
         <v>119254432</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,37 +1228,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119253683</v>
+        <v>119253637</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 35419-2024 artfynd.xlsx
+++ b/artfynd/A 35419-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253683</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253676</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253663</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254435</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254432</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,8 +1362,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>